--- a/src/views/game/zlzq/cardList/dahetaoCard/z_level.xlsx
+++ b/src/views/game/zlzq/cardList/dahetaoCard/z_level.xlsx
@@ -1,16 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="11790" windowHeight="10800" firstSheet="1"/>
+    <workbookView windowWidth="14550" windowHeight="10830" firstSheet="1" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="蛮石" sheetId="8" r:id="rId1"/>
-    <sheet name="帝国" sheetId="5" r:id="rId2"/>
-    <sheet name="隐秘" sheetId="7" r:id="rId3"/>
+    <sheet name="隐秘" sheetId="7" r:id="rId2"/>
+    <sheet name="帝国" sheetId="5" r:id="rId3"/>
     <sheet name="禅意" sheetId="6" r:id="rId4"/>
+    <sheet name="大核桃" sheetId="9" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="74">
   <si>
     <t>名称</t>
   </si>
@@ -68,12 +69,12 @@
     <t>肥鼠晚宴</t>
   </si>
   <si>
+    <t>符文·噬人花田</t>
+  </si>
+  <si>
     <t>飞斧狂人</t>
   </si>
   <si>
-    <t>飞斧女豪</t>
-  </si>
-  <si>
     <t>贪食白龙</t>
   </si>
   <si>
@@ -104,13 +105,67 @@
     <t>蛮石卡等：</t>
   </si>
   <si>
+    <t>电流激活</t>
+  </si>
+  <si>
+    <t>沉重否定</t>
+  </si>
+  <si>
+    <t>全数否定</t>
+  </si>
+  <si>
+    <t>隐形术</t>
+  </si>
+  <si>
+    <t>破魔系教授</t>
+  </si>
+  <si>
+    <t>传记·海市蜃楼·蛇</t>
+  </si>
+  <si>
+    <t>克隆术</t>
+  </si>
+  <si>
+    <t>学仆-脉冲型</t>
+  </si>
+  <si>
+    <t>幻域秘树</t>
+  </si>
+  <si>
+    <t>幻象巨龙</t>
+  </si>
+  <si>
+    <t>米拉方舟</t>
+  </si>
+  <si>
+    <t>No.4希尔伯特</t>
+  </si>
+  <si>
+    <t>No.5咒刃·布雷克</t>
+  </si>
+  <si>
+    <t>鬼童-7号</t>
+  </si>
+  <si>
+    <t>No.2时光·米拉</t>
+  </si>
+  <si>
+    <t>No.6沃凡瑞拉</t>
+  </si>
+  <si>
+    <t>隐秘卡等：</t>
+  </si>
+  <si>
     <t>圣殿斥候</t>
   </si>
   <si>
     <t>圣殿弩手</t>
   </si>
   <si>
-    <t>田园守望者</t>
+    <t>田园守望者1</t>
+  </si>
+  <si>
+    <t>田园守望者2</t>
   </si>
   <si>
     <t>增援战线</t>
@@ -122,9 +177,6 @@
     <t>四芒军旗</t>
   </si>
   <si>
-    <t>传记·钢铁守卫</t>
-  </si>
-  <si>
     <t>圣殿御卫</t>
   </si>
   <si>
@@ -155,61 +207,10 @@
     <t>帝国卡等：</t>
   </si>
   <si>
-    <t>洞悉之眼</t>
-  </si>
-  <si>
-    <t>电流激活</t>
-  </si>
-  <si>
-    <t>沉重否定</t>
-  </si>
-  <si>
-    <t>全数否定</t>
-  </si>
-  <si>
-    <t>隐形术</t>
-  </si>
-  <si>
-    <t>破魔系教授</t>
-  </si>
-  <si>
-    <t>传记·海市蜃楼·蛇</t>
-  </si>
-  <si>
-    <t>克隆术</t>
-  </si>
-  <si>
-    <t>学仆-脉冲型</t>
-  </si>
-  <si>
-    <t>幻域秘树</t>
-  </si>
-  <si>
-    <t>观星台大预言家</t>
-  </si>
-  <si>
-    <t>幻象巨龙</t>
-  </si>
-  <si>
-    <t>米拉方舟</t>
-  </si>
-  <si>
-    <t>No.8雷鸣·泰拉德</t>
-  </si>
-  <si>
-    <t>鬼童-7号</t>
-  </si>
-  <si>
-    <t>No.2时光·米拉</t>
-  </si>
-  <si>
-    <t>No.6沃凡瑞拉</t>
-  </si>
-  <si>
-    <t>隐秘卡等：</t>
-  </si>
-  <si>
-    <t>长耳庄巧姑</t>
+    <t>雪庐草人</t>
+  </si>
+  <si>
+    <t>苦行武僧</t>
   </si>
   <si>
     <t>飓风术</t>
@@ -218,10 +219,10 @@
     <t>太极剑法</t>
   </si>
   <si>
-    <t>龟族僧人</t>
-  </si>
-  <si>
-    <t>连击</t>
+    <t>连击1</t>
+  </si>
+  <si>
+    <t>连击2</t>
   </si>
   <si>
     <t>铁山靠</t>
@@ -230,10 +231,19 @@
     <t>风卷残云</t>
   </si>
   <si>
+    <t>蟠桃隐士</t>
+  </si>
+  <si>
+    <t>御风武者</t>
+  </si>
+  <si>
     <t>墨轩隐士</t>
   </si>
   <si>
-    <t>萌化术</t>
+    <t>万物之灵</t>
+  </si>
+  <si>
+    <t>符文·如来神掌</t>
   </si>
   <si>
     <t>神机玄女·轩</t>
@@ -1214,7 +1224,7 @@
     <col min="3" max="3" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1225,7 +1235,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -1236,7 +1246,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1247,7 +1257,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
@@ -1255,15 +1265,15 @@
         <v>4</v>
       </c>
       <c r="C4" s="1">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:4">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
@@ -1277,11 +1287,11 @@
       </c>
       <c r="C7" s="1">
         <f>AVERAGE(C2:C4)</f>
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D7" s="2"/>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
         <v>8</v>
       </c>
@@ -1292,7 +1302,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
         <v>9</v>
       </c>
@@ -1303,7 +1313,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:4">
       <c r="A12" s="2" t="s">
         <v>10</v>
       </c>
@@ -1314,7 +1324,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:4">
       <c r="A13" s="2" t="s">
         <v>11</v>
       </c>
@@ -1325,29 +1335,29 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B14" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C14" s="2">
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B15" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C15" s="2">
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
         <v>14</v>
       </c>
@@ -1388,7 +1398,7 @@
         <v>3</v>
       </c>
       <c r="C22" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1421,7 +1431,7 @@
         <v>5</v>
       </c>
       <c r="C25" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1432,7 +1442,7 @@
         <v>6</v>
       </c>
       <c r="C26" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1454,7 +1464,7 @@
       </c>
       <c r="C29" s="3">
         <f>AVERAGE(C22:C26)</f>
-        <v>20.8</v>
+        <v>21.4</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1481,12 +1491,12 @@
   <dimension ref="A1:D33"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="16.375" customWidth="1"/>
+    <col min="1" max="1" width="17.75" customWidth="1"/>
     <col min="2" max="2" width="11" customWidth="1"/>
     <col min="3" max="3" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1497,7 +1507,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
         <v>24</v>
       </c>
@@ -1508,18 +1518,18 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
         <v>25</v>
       </c>
       <c r="B3" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C3" s="1">
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
         <v>26</v>
       </c>
@@ -1530,101 +1540,101 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="1" t="s">
+    <row r="5" spans="1:4">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="1">
+        <f>AVERAGE(C2:C4)</f>
+        <v>22</v>
+      </c>
+      <c r="D7" s="2"/>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="1">
-        <v>3</v>
-      </c>
-      <c r="C5" s="1">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="1" t="s">
+      <c r="B10" s="2">
+        <v>1</v>
+      </c>
+      <c r="C10" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B6" s="1">
-        <v>5</v>
-      </c>
-      <c r="C6" s="1">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="1">
-        <f>AVERAGE(C2:C6)</f>
-        <v>21.4</v>
-      </c>
-      <c r="D9" s="2"/>
-    </row>
-    <row r="12" spans="1:3">
+      <c r="B11" s="2">
+        <v>2</v>
+      </c>
+      <c r="C11" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
       <c r="A12" s="2" t="s">
         <v>29</v>
       </c>
       <c r="B12" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C12" s="2">
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:4">
       <c r="A13" s="2" t="s">
         <v>30</v>
       </c>
       <c r="B13" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B14" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C14" s="2">
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
         <v>32</v>
       </c>
       <c r="B15" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
         <v>33</v>
       </c>
       <c r="B16" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C16" s="2">
         <v>22</v>
@@ -1635,7 +1645,7 @@
         <v>34</v>
       </c>
       <c r="B17" s="2">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C17" s="2">
         <v>22</v>
@@ -1659,8 +1669,8 @@
         <v>15</v>
       </c>
       <c r="C20" s="2">
-        <f>AVERAGE(C12:C17)</f>
-        <v>22</v>
+        <f>AVERAGE(C10:C17)</f>
+        <v>21.375</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1668,10 +1678,10 @@
         <v>35</v>
       </c>
       <c r="B23" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C23" s="3">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1679,10 +1689,10 @@
         <v>36</v>
       </c>
       <c r="B24" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C24" s="3">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1693,7 +1703,7 @@
         <v>4</v>
       </c>
       <c r="C25" s="3">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1701,10 +1711,10 @@
         <v>38</v>
       </c>
       <c r="B26" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C26" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1712,10 +1722,10 @@
         <v>39</v>
       </c>
       <c r="B27" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C27" s="3">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1737,7 +1747,7 @@
       </c>
       <c r="C30" s="3">
         <f>AVERAGE(C23:C27)</f>
-        <v>18.2</v>
+        <v>20.6</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -1748,8 +1758,8 @@
         <v>40</v>
       </c>
       <c r="C33" s="4">
-        <f>AVERAGE(C2:C6,C12:C17,C23:C27)</f>
-        <v>20.625</v>
+        <f>AVERAGE(C2:C4,C10:C17,C23:C27)</f>
+        <v>21.25</v>
       </c>
     </row>
   </sheetData>
@@ -1761,15 +1771,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="17.75" customWidth="1"/>
+    <col min="1" max="1" width="16.375" customWidth="1"/>
     <col min="2" max="2" width="11" customWidth="1"/>
     <col min="3" max="3" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1780,53 +1790,53 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
         <v>41</v>
       </c>
       <c r="B2" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C2" s="1">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
         <v>42</v>
       </c>
       <c r="B3" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C3" s="1">
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
         <v>43</v>
       </c>
       <c r="B4" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" s="1">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B5" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" s="1">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B6" s="1">
         <v>3</v>
@@ -1835,54 +1845,54 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-    </row>
-    <row r="8" spans="1:3">
+    <row r="7" spans="1:4">
+      <c r="A7" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B7" s="1">
+        <v>5</v>
+      </c>
+      <c r="C7" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
     </row>
     <row r="9" spans="1:4">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="1">
-        <f>AVERAGE(C2:C6)</f>
-        <v>19.8</v>
-      </c>
-      <c r="D9" s="2"/>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B12" s="2">
+      <c r="C10" s="1">
+        <f>AVERAGE(C2:C7)</f>
+        <v>22</v>
+      </c>
+      <c r="D10" s="2"/>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B13" s="2">
         <v>1</v>
       </c>
-      <c r="C12" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B13" s="2">
-        <v>2</v>
-      </c>
       <c r="C13" s="2">
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B14" s="2">
         <v>2</v>
@@ -1891,20 +1901,20 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B15" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C15" s="2">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B16" s="2">
         <v>3</v>
@@ -1915,76 +1925,76 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B17" s="2">
         <v>4</v>
       </c>
       <c r="C17" s="2">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B18" s="2">
-        <v>5</v>
-      </c>
-      <c r="C18" s="2">
-        <v>17</v>
-      </c>
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B19" s="2">
-        <v>6</v>
-      </c>
-      <c r="C19" s="2">
-        <v>22</v>
-      </c>
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C20" s="2">
+        <f>AVERAGE(C13:C17)</f>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B23" s="3">
+        <v>3</v>
+      </c>
+      <c r="C23" s="3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B20" s="2">
-        <v>7</v>
-      </c>
-      <c r="C20" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="2"/>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C23" s="2">
-        <f>AVERAGE(C12:C20)</f>
-        <v>20.7777777777778</v>
+      <c r="B24" s="3">
+        <v>4</v>
+      </c>
+      <c r="C24" s="3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B25" s="3">
+        <v>4</v>
+      </c>
+      <c r="C25" s="3">
+        <v>18</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B26" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C26" s="3">
         <v>20</v>
@@ -1992,69 +2002,47 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B27" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C27" s="3">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="28" spans="1:3">
-      <c r="A28" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="B28" s="3">
-        <v>5</v>
-      </c>
-      <c r="C28" s="3">
-        <v>19</v>
-      </c>
+      <c r="A28" s="3"/>
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
     </row>
     <row r="29" spans="1:3">
-      <c r="A29" s="3" t="s">
+      <c r="A29" s="3"/>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C30" s="3">
+        <f>AVERAGE(C23:C27)</f>
+        <v>19.2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B33" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="B29" s="3">
-        <v>7</v>
-      </c>
-      <c r="C29" s="3">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" s="3"/>
-      <c r="B30" s="3"/>
-      <c r="C30" s="3"/>
-    </row>
-    <row r="31" spans="1:3">
-      <c r="A31" s="3"/>
-      <c r="B31" s="3"/>
-      <c r="C31" s="3"/>
-    </row>
-    <row r="32" spans="1:3">
-      <c r="A32" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C32" s="3">
-        <f>AVERAGE(C26:C29)</f>
-        <v>20.5</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3">
-      <c r="A35" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="C35" s="4">
-        <f>AVERAGE(C2:C6,C12:C20,C26:C29)</f>
-        <v>20.4444444444444</v>
+      <c r="C33" s="4">
+        <f>AVERAGE(C2:C7,C13:C17,C23:C27)</f>
+        <v>21.125</v>
       </c>
     </row>
   </sheetData>
@@ -2074,7 +2062,7 @@
     <col min="3" max="3" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2085,51 +2073,51 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B2" s="1">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="1" t="s">
         <v>59</v>
-      </c>
-      <c r="B2" s="1">
-        <v>2</v>
-      </c>
-      <c r="C2" s="1">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>60</v>
       </c>
       <c r="B3" s="1">
         <v>2</v>
       </c>
       <c r="C3" s="1">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B4" s="1">
         <v>2</v>
       </c>
       <c r="C4" s="1">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
         <v>61</v>
       </c>
       <c r="B5" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5" s="1">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
         <v>62</v>
       </c>
@@ -2140,7 +2128,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
         <v>63</v>
       </c>
@@ -2148,108 +2136,102 @@
         <v>3</v>
       </c>
       <c r="C7" s="1">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B8" s="1">
         <v>3</v>
       </c>
       <c r="C8" s="1">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B9" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C9" s="1">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B10" s="1">
-        <v>3</v>
-      </c>
-      <c r="C10" s="1">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B11" s="1">
-        <v>3</v>
-      </c>
-      <c r="C11" s="1">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+    </row>
+    <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B12" s="1">
+        <v>6</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="1">
+        <f>AVERAGE(C2:C9)</f>
+        <v>18.625</v>
+      </c>
+      <c r="D12" s="2"/>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B15" s="2">
+        <v>2</v>
+      </c>
+      <c r="C15" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B16" s="2">
         <v>4</v>
       </c>
-      <c r="C12" s="1">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C15" s="1">
-        <f>AVERAGE(C2:C12)</f>
-        <v>13.8181818181818</v>
-      </c>
-      <c r="D15" s="2"/>
+      <c r="C16" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B17" s="2">
+        <v>4</v>
+      </c>
+      <c r="C17" s="2">
+        <v>19</v>
+      </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B18" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C18" s="2">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B19" s="2">
-        <v>4</v>
-      </c>
-      <c r="C19" s="2">
-        <v>12</v>
-      </c>
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2"/>
@@ -2257,42 +2239,48 @@
       <c r="C20" s="2"/>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="2" t="s">
+      <c r="A21" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B21" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C22" s="2">
-        <f>AVERAGE(C18:C19)</f>
+      <c r="C21" s="2">
+        <f>AVERAGE(C15:C18)</f>
+        <v>19.75</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B24" s="3">
+        <v>3</v>
+      </c>
+      <c r="C24" s="3">
         <v>12</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B25" s="3">
         <v>4</v>
       </c>
       <c r="C25" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B26" s="3">
         <v>4</v>
       </c>
       <c r="C26" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -2313,8 +2301,8 @@
         <v>21</v>
       </c>
       <c r="C29" s="3">
-        <f>AVERAGE(C25:C26)</f>
-        <v>17</v>
+        <f>AVERAGE(C24:C26)</f>
+        <v>16</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -2322,15 +2310,26 @@
         <v>22</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C32" s="4">
-        <f>AVERAGE(C2:C12,C18:C19,C25:C26)</f>
-        <v>14</v>
+        <f>AVERAGE(C2:C9,C15:C18,C24:C26)</f>
+        <v>18.4</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/src/views/game/zlzq/cardList/dahetaoCard/z_level.xlsx
+++ b/src/views/game/zlzq/cardList/dahetaoCard/z_level.xlsx
@@ -4,12 +4,12 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="14550" windowHeight="10830" firstSheet="1" activeTab="2"/>
+    <workbookView windowWidth="11910" windowHeight="11745" firstSheet="1" activeTab="2"/>
   </bookViews>
   <sheets>
-    <sheet name="蛮石" sheetId="8" r:id="rId1"/>
-    <sheet name="隐秘" sheetId="7" r:id="rId2"/>
-    <sheet name="帝国" sheetId="5" r:id="rId3"/>
+    <sheet name="帝国" sheetId="5" r:id="rId1"/>
+    <sheet name="蛮石" sheetId="8" r:id="rId2"/>
+    <sheet name="隐秘" sheetId="7" r:id="rId3"/>
     <sheet name="禅意" sheetId="6" r:id="rId4"/>
     <sheet name="大核桃" sheetId="9" r:id="rId5"/>
   </sheets>
@@ -42,21 +42,81 @@
     <t>卡等</t>
   </si>
   <si>
+    <t>圣殿斥候</t>
+  </si>
+  <si>
+    <t>圣殿卫士</t>
+  </si>
+  <si>
+    <t>天使琼浆</t>
+  </si>
+  <si>
+    <t>田园守望者1</t>
+  </si>
+  <si>
+    <t>田园守望者2</t>
+  </si>
+  <si>
+    <t>增援战线</t>
+  </si>
+  <si>
+    <t>光明惩戒</t>
+  </si>
+  <si>
+    <t>小计：</t>
+  </si>
+  <si>
+    <t>蓝色卡等：</t>
+  </si>
+  <si>
+    <t>四芒军旗</t>
+  </si>
+  <si>
+    <t>圣殿御卫</t>
+  </si>
+  <si>
+    <t>白袍主教</t>
+  </si>
+  <si>
+    <t>召集护卫</t>
+  </si>
+  <si>
+    <t>惩戒天使</t>
+  </si>
+  <si>
+    <t>紫色卡等：</t>
+  </si>
+  <si>
+    <t>曙光·安娜贝尔</t>
+  </si>
+  <si>
+    <t>明日之音·露娜</t>
+  </si>
+  <si>
+    <t>正阳大主教·伊恩</t>
+  </si>
+  <si>
+    <t>橙色卡等：</t>
+  </si>
+  <si>
+    <t>总计：</t>
+  </si>
+  <si>
+    <t>帝国卡等：</t>
+  </si>
+  <si>
     <t>旷野祭师</t>
   </si>
   <si>
     <t>势如破竹</t>
   </si>
   <si>
+    <t>旷野猎手</t>
+  </si>
+  <si>
     <t>强行捕猎</t>
   </si>
   <si>
-    <t>小计：</t>
-  </si>
-  <si>
-    <t>蓝色卡等：</t>
-  </si>
-  <si>
     <t>暴怒野人</t>
   </si>
   <si>
@@ -69,7 +129,7 @@
     <t>肥鼠晚宴</t>
   </si>
   <si>
-    <t>符文·噬人花田</t>
+    <t>符文·源力之石</t>
   </si>
   <si>
     <t>飞斧狂人</t>
@@ -78,12 +138,6 @@
     <t>贪食白龙</t>
   </si>
   <si>
-    <t>紫色卡等：</t>
-  </si>
-  <si>
-    <t>鸵鸟王·霍利</t>
-  </si>
-  <si>
     <t>旷野游侠·大羽</t>
   </si>
   <si>
@@ -96,16 +150,13 @@
     <t>蛮古撼地兽</t>
   </si>
   <si>
-    <t>橙色卡等：</t>
-  </si>
-  <si>
-    <t>总计：</t>
-  </si>
-  <si>
     <t>蛮石卡等：</t>
   </si>
   <si>
-    <t>电流激活</t>
+    <t>洞悉之眼</t>
+  </si>
+  <si>
+    <t>学仆-观测型</t>
   </si>
   <si>
     <t>沉重否定</t>
@@ -120,27 +171,27 @@
     <t>破魔系教授</t>
   </si>
   <si>
-    <t>传记·海市蜃楼·蛇</t>
-  </si>
-  <si>
-    <t>克隆术</t>
-  </si>
-  <si>
-    <t>学仆-脉冲型</t>
-  </si>
-  <si>
-    <t>幻域秘树</t>
-  </si>
-  <si>
-    <t>幻象巨龙</t>
+    <t>克隆术1</t>
+  </si>
+  <si>
+    <t>克隆术2</t>
+  </si>
+  <si>
+    <t>学仆-脉冲型1</t>
+  </si>
+  <si>
+    <t>学仆-脉冲型2</t>
+  </si>
+  <si>
+    <t>学仆-脉冲型3</t>
+  </si>
+  <si>
+    <t>观星台大预言家</t>
   </si>
   <si>
     <t>米拉方舟</t>
   </si>
   <si>
-    <t>No.4希尔伯特</t>
-  </si>
-  <si>
     <t>No.5咒刃·布雷克</t>
   </si>
   <si>
@@ -154,57 +205,6 @@
   </si>
   <si>
     <t>隐秘卡等：</t>
-  </si>
-  <si>
-    <t>圣殿斥候</t>
-  </si>
-  <si>
-    <t>圣殿弩手</t>
-  </si>
-  <si>
-    <t>田园守望者1</t>
-  </si>
-  <si>
-    <t>田园守望者2</t>
-  </si>
-  <si>
-    <t>增援战线</t>
-  </si>
-  <si>
-    <t>光明惩戒</t>
-  </si>
-  <si>
-    <t>四芒军旗</t>
-  </si>
-  <si>
-    <t>圣殿御卫</t>
-  </si>
-  <si>
-    <t>白袍主教</t>
-  </si>
-  <si>
-    <t>圣殿骑士</t>
-  </si>
-  <si>
-    <t>召集护卫</t>
-  </si>
-  <si>
-    <t>曙光·安娜贝尔</t>
-  </si>
-  <si>
-    <t>圣枪·卡洛琳</t>
-  </si>
-  <si>
-    <t>明日之音·露娜</t>
-  </si>
-  <si>
-    <t>正阳大主教·伊恩</t>
-  </si>
-  <si>
-    <t>钢铁统帅·雷蒙德</t>
-  </si>
-  <si>
-    <t>帝国卡等：</t>
   </si>
   <si>
     <t>雪庐草人</t>
@@ -1240,7 +1240,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2" s="1">
         <v>22</v>
@@ -1262,85 +1262,85 @@
         <v>5</v>
       </c>
       <c r="B4" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C4" s="1">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="1">
+        <v>3</v>
+      </c>
+      <c r="C5" s="1">
+        <v>22</v>
+      </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
+      <c r="A6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="1">
+        <v>3</v>
+      </c>
+      <c r="C6" s="1">
+        <v>22</v>
+      </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="B7" s="1">
+        <v>3</v>
       </c>
       <c r="C7" s="1">
-        <f>AVERAGE(C2:C4)</f>
-        <v>21</v>
-      </c>
-      <c r="D7" s="2"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="1">
+        <v>5</v>
+      </c>
+      <c r="C8" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" s="2">
-        <v>2</v>
-      </c>
-      <c r="C10" s="2">
-        <v>22</v>
-      </c>
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" s="2">
-        <v>2</v>
-      </c>
-      <c r="C11" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="2" t="s">
+      <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="2">
-        <v>3</v>
-      </c>
-      <c r="C12" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="2" t="s">
+      <c r="B11" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="2">
-        <v>3</v>
-      </c>
-      <c r="C13" s="2">
-        <v>22</v>
-      </c>
+      <c r="C11" s="1">
+        <f>AVERAGE(C2:C8)</f>
+        <v>22</v>
+      </c>
+      <c r="D11" s="2"/>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B14" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C14" s="2">
         <v>22</v>
@@ -1351,7 +1351,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" s="2">
         <v>22</v>
@@ -1362,54 +1362,54 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C16" s="2">
         <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
+      <c r="A17" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="2">
+        <v>4</v>
+      </c>
+      <c r="C17" s="2">
+        <v>22</v>
+      </c>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
+      <c r="A18" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="2">
+        <v>6</v>
+      </c>
+      <c r="C18" s="2">
+        <v>22</v>
+      </c>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C19" s="2">
-        <f>AVERAGE(C10:C16)</f>
-        <v>22</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B22" s="3">
-        <v>3</v>
-      </c>
-      <c r="C22" s="3">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="3" t="s">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B23" s="3">
-        <v>3</v>
-      </c>
-      <c r="C23" s="3">
-        <v>20</v>
+      <c r="C21" s="2">
+        <f>AVERAGE(C14:C18)</f>
+        <v>22</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1417,10 +1417,10 @@
         <v>18</v>
       </c>
       <c r="B24" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C24" s="3">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1428,10 +1428,10 @@
         <v>19</v>
       </c>
       <c r="B25" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C25" s="3">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1442,7 +1442,7 @@
         <v>6</v>
       </c>
       <c r="C26" s="3">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1457,14 +1457,14 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="3" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>21</v>
       </c>
       <c r="C29" s="3">
-        <f>AVERAGE(C22:C26)</f>
-        <v>21.4</v>
+        <f>AVERAGE(C24:C26)</f>
+        <v>19.6666666666667</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1475,8 +1475,8 @@
         <v>23</v>
       </c>
       <c r="C32" s="4">
-        <f>AVERAGE(C2:C4,C10:C16,C22:C26)</f>
-        <v>21.6</v>
+        <f>AVERAGE(C2:C8,C14:C18,C24:C26)</f>
+        <v>21.5333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -1488,7 +1488,279 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D32"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <cols>
+    <col min="1" max="1" width="16.375" customWidth="1"/>
+    <col min="2" max="2" width="11" customWidth="1"/>
+    <col min="3" max="3" width="11.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="1">
+        <v>2</v>
+      </c>
+      <c r="C2" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" s="1">
+        <v>2</v>
+      </c>
+      <c r="C3" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="1">
+        <v>2</v>
+      </c>
+      <c r="C4" s="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="1">
+        <v>4</v>
+      </c>
+      <c r="C5" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="1">
+        <f>AVERAGE(C2:C5)</f>
+        <v>21.75</v>
+      </c>
+      <c r="D8" s="2"/>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="2">
+        <v>2</v>
+      </c>
+      <c r="C11" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" s="2">
+        <v>2</v>
+      </c>
+      <c r="C12" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B13" s="2">
+        <v>3</v>
+      </c>
+      <c r="C13" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B14" s="2">
+        <v>3</v>
+      </c>
+      <c r="C14" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" s="2">
+        <v>3</v>
+      </c>
+      <c r="C15" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B16" s="2">
+        <v>4</v>
+      </c>
+      <c r="C16" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B17" s="2">
+        <v>8</v>
+      </c>
+      <c r="C17" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20" s="2">
+        <f>AVERAGE(C11:C17)</f>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B23" s="3">
+        <v>3</v>
+      </c>
+      <c r="C23" s="3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B24" s="3">
+        <v>4</v>
+      </c>
+      <c r="C24" s="3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" s="3">
+        <v>5</v>
+      </c>
+      <c r="C25" s="3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="3">
+        <v>6</v>
+      </c>
+      <c r="C26" s="3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="3"/>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="3"/>
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C29" s="3">
+        <f>AVERAGE(C23:C26)</f>
+        <v>21.75</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C32" s="4">
+        <f>AVERAGE(C2:C5,C11:C17,C23:C26)</f>
+        <v>21.4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="17.75" customWidth="1"/>
@@ -1509,18 +1781,18 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="B2" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2" s="1">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="B3" s="1">
         <v>2</v>
@@ -1531,19 +1803,25 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="B4" s="1">
+        <v>2</v>
+      </c>
+      <c r="C4" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5" s="1">
         <v>3</v>
       </c>
-      <c r="C4" s="1">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
+      <c r="C5" s="1">
+        <v>22</v>
+      </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1"/>
@@ -1551,35 +1829,29 @@
       <c r="C6" s="1"/>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="1">
-        <f>AVERAGE(C2:C4)</f>
-        <v>22</v>
-      </c>
-      <c r="D7" s="2"/>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B10" s="2">
-        <v>1</v>
-      </c>
-      <c r="C10" s="2">
-        <v>22</v>
-      </c>
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="1">
+        <f>AVERAGE(C2:C5)</f>
+        <v>21.5</v>
+      </c>
+      <c r="D8" s="2"/>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="B11" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C11" s="2">
         <v>22</v>
@@ -1587,7 +1859,7 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="B12" s="2">
         <v>2</v>
@@ -1598,43 +1870,43 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="B13" s="2">
         <v>2</v>
       </c>
       <c r="C13" s="2">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="B14" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" s="2">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="B15" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C15" s="2">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="B16" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C16" s="2">
         <v>22</v>
@@ -1642,65 +1914,65 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="B17" s="2">
+        <v>3</v>
+      </c>
+      <c r="C17" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B18" s="2">
+        <v>5</v>
+      </c>
+      <c r="C18" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B19" s="2">
         <v>7</v>
       </c>
-      <c r="C17" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
+      <c r="C19" s="2">
+        <v>22</v>
+      </c>
     </row>
     <row r="20" spans="1:3">
-      <c r="A20" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C20" s="2">
-        <f>AVERAGE(C10:C17)</f>
-        <v>21.375</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B23" s="3">
-        <v>2</v>
-      </c>
-      <c r="C23" s="3">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B24" s="3">
-        <v>3</v>
-      </c>
-      <c r="C24" s="3">
-        <v>21</v>
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C22" s="2">
+        <f>AVERAGE(C11:C19)</f>
+        <v>20.4444444444444</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="3" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="B25" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C25" s="3">
         <v>22</v>
@@ -1708,30 +1980,36 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="3" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="B26" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C26" s="3">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="3" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="B27" s="3">
+        <v>5</v>
+      </c>
+      <c r="C27" s="3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B28" s="3">
         <v>7</v>
       </c>
-      <c r="C27" s="3">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" s="3"/>
-      <c r="B28" s="3"/>
-      <c r="C28" s="3"/>
+      <c r="C28" s="3">
+        <v>22</v>
+      </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="3"/>
@@ -1739,310 +2017,32 @@
       <c r="C29" s="3"/>
     </row>
     <row r="30" spans="1:3">
-      <c r="A30" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B30" s="3" t="s">
+      <c r="A30" s="3"/>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B31" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C30" s="3">
-        <f>AVERAGE(C23:C27)</f>
-        <v>20.6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C33" s="4">
-        <f>AVERAGE(C2:C4,C10:C17,C23:C27)</f>
-        <v>21.25</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:D33"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
-  <cols>
-    <col min="1" max="1" width="16.375" customWidth="1"/>
-    <col min="2" max="2" width="11" customWidth="1"/>
-    <col min="3" max="3" width="11.5" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B2" s="1">
-        <v>1</v>
-      </c>
-      <c r="C2" s="1">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B3" s="1">
-        <v>3</v>
-      </c>
-      <c r="C3" s="1">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B4" s="1">
-        <v>3</v>
-      </c>
-      <c r="C4" s="1">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B5" s="1">
-        <v>3</v>
-      </c>
-      <c r="C5" s="1">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B6" s="1">
-        <v>3</v>
-      </c>
-      <c r="C6" s="1">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B7" s="1">
-        <v>5</v>
-      </c>
-      <c r="C7" s="1">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="1">
-        <f>AVERAGE(C2:C7)</f>
-        <v>22</v>
-      </c>
-      <c r="D10" s="2"/>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B13" s="2">
-        <v>1</v>
-      </c>
-      <c r="C13" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B14" s="2">
-        <v>2</v>
-      </c>
-      <c r="C14" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B15" s="2">
-        <v>3</v>
-      </c>
-      <c r="C15" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B16" s="2">
-        <v>3</v>
-      </c>
-      <c r="C16" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B17" s="2">
-        <v>4</v>
-      </c>
-      <c r="C17" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C20" s="2">
-        <f>AVERAGE(C13:C17)</f>
-        <v>22</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B23" s="3">
-        <v>3</v>
-      </c>
-      <c r="C23" s="3">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="B24" s="3">
-        <v>4</v>
-      </c>
-      <c r="C24" s="3">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="B25" s="3">
-        <v>4</v>
-      </c>
-      <c r="C25" s="3">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B26" s="3">
-        <v>6</v>
-      </c>
-      <c r="C26" s="3">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="B27" s="3">
-        <v>8</v>
-      </c>
-      <c r="C27" s="3">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" s="3"/>
-      <c r="B28" s="3"/>
-      <c r="C28" s="3"/>
-    </row>
-    <row r="29" spans="1:3">
-      <c r="A29" s="3"/>
-      <c r="B29" s="3"/>
-      <c r="C29" s="3"/>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C30" s="3">
-        <f>AVERAGE(C23:C27)</f>
-        <v>19.2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B33" s="4" t="s">
+      <c r="C31" s="3">
+        <f>AVERAGE(C25:C28)</f>
+        <v>21.5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B34" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="C33" s="4">
-        <f>AVERAGE(C2:C7,C13:C17,C23:C27)</f>
-        <v>21.125</v>
+      <c r="C34" s="4">
+        <f>AVERAGE(C2:C5,C11:C19,C25:C28)</f>
+        <v>20.9411764705882</v>
       </c>
     </row>
   </sheetData>
@@ -2173,10 +2173,10 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C12" s="1">
         <f>AVERAGE(C2:C9)</f>
@@ -2240,10 +2240,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C21" s="2">
         <f>AVERAGE(C15:C18)</f>
@@ -2295,7 +2295,7 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="3" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>21</v>

--- a/src/views/game/zlzq/cardList/dahetaoCard/z_level.xlsx
+++ b/src/views/game/zlzq/cardList/dahetaoCard/z_level.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\code\keyuanWeb\src\views\game\zlzq\cardList\dahetaoCard\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="11910" windowHeight="11745" firstSheet="1" activeTab="2"/>
+    <workbookView windowWidth="11985" windowHeight="9795" firstSheet="1" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="帝国" sheetId="5" r:id="rId1"/>
@@ -60,7 +65,10 @@
     <t>增援战线</t>
   </si>
   <si>
-    <t>光明惩戒</t>
+    <t>光明惩戒1</t>
+  </si>
+  <si>
+    <t>光明惩戒2</t>
   </si>
   <si>
     <t>小计：</t>
@@ -72,30 +80,27 @@
     <t>四芒军旗</t>
   </si>
   <si>
-    <t>圣殿御卫</t>
-  </si>
-  <si>
-    <t>白袍主教</t>
-  </si>
-  <si>
     <t>召集护卫</t>
   </si>
   <si>
-    <t>惩戒天使</t>
-  </si>
-  <si>
     <t>紫色卡等：</t>
   </si>
   <si>
     <t>曙光·安娜贝尔</t>
   </si>
   <si>
+    <t>圣枪·卡洛琳</t>
+  </si>
+  <si>
     <t>明日之音·露娜</t>
   </si>
   <si>
     <t>正阳大主教·伊恩</t>
   </si>
   <si>
+    <t>钢铁统帅·雷蒙德</t>
+  </si>
+  <si>
     <t>橙色卡等：</t>
   </si>
   <si>
@@ -105,15 +110,12 @@
     <t>帝国卡等：</t>
   </si>
   <si>
-    <t>旷野祭师</t>
+    <t>旷野猎手</t>
   </si>
   <si>
     <t>势如破竹</t>
   </si>
   <si>
-    <t>旷野猎手</t>
-  </si>
-  <si>
     <t>强行捕猎</t>
   </si>
   <si>
@@ -150,12 +152,12 @@
     <t>蛮古撼地兽</t>
   </si>
   <si>
+    <t>原野大祭师·鲁玛</t>
+  </si>
+  <si>
     <t>蛮石卡等：</t>
   </si>
   <si>
-    <t>洞悉之眼</t>
-  </si>
-  <si>
     <t>学仆-观测型</t>
   </si>
   <si>
@@ -177,13 +179,16 @@
     <t>克隆术2</t>
   </si>
   <si>
-    <t>学仆-脉冲型1</t>
-  </si>
-  <si>
-    <t>学仆-脉冲型2</t>
-  </si>
-  <si>
-    <t>学仆-脉冲型3</t>
+    <t>学仆-脉冲型</t>
+  </si>
+  <si>
+    <t>符文·邪月之夜</t>
+  </si>
+  <si>
+    <t>符文·雷火核心</t>
+  </si>
+  <si>
+    <t>幻域秘树</t>
   </si>
   <si>
     <t>观星台大预言家</t>
@@ -1243,7 +1248,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="1">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1254,7 +1259,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="1">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1276,7 +1281,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="1">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1287,7 +1292,7 @@
         <v>3</v>
       </c>
       <c r="C6" s="1">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1298,7 +1303,7 @@
         <v>3</v>
       </c>
       <c r="C7" s="1">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1313,9 +1318,15 @@
       </c>
     </row>
     <row r="9" spans="1:4">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
+      <c r="A9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="1">
+        <v>5</v>
+      </c>
+      <c r="C9" s="1">
+        <v>19</v>
+      </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1"/>
@@ -1323,38 +1334,32 @@
       <c r="C10" s="1"/>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11" s="1" t="s">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="1">
-        <f>AVERAGE(C2:C8)</f>
-        <v>22</v>
-      </c>
-      <c r="D11" s="2"/>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="2" t="s">
+      <c r="B12" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="2">
-        <v>1</v>
-      </c>
-      <c r="C14" s="2">
-        <v>22</v>
-      </c>
+      <c r="C12" s="1">
+        <f>AVERAGE(C2:C9)</f>
+        <v>21.5</v>
+      </c>
+      <c r="D12" s="2"/>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B15" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C15" s="2">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -1362,54 +1367,54 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" s="2">
         <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="2">
+      <c r="C19" s="2">
+        <f>AVERAGE(C15:C16)</f>
+        <v>20.5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B22" s="3">
+        <v>3</v>
+      </c>
+      <c r="C22" s="3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B23" s="3">
         <v>4</v>
       </c>
-      <c r="C17" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B18" s="2">
-        <v>6</v>
-      </c>
-      <c r="C18" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C21" s="2">
-        <f>AVERAGE(C14:C18)</f>
-        <v>22</v>
+      <c r="C23" s="3">
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1417,10 +1422,10 @@
         <v>18</v>
       </c>
       <c r="B24" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C24" s="3">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1428,10 +1433,10 @@
         <v>19</v>
       </c>
       <c r="B25" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C25" s="3">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1439,10 +1444,10 @@
         <v>20</v>
       </c>
       <c r="B26" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C26" s="3">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1457,14 +1462,14 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>21</v>
       </c>
       <c r="C29" s="3">
-        <f>AVERAGE(C24:C26)</f>
-        <v>19.6666666666667</v>
+        <f>AVERAGE(C22:C26)</f>
+        <v>19.2</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1475,8 +1480,8 @@
         <v>23</v>
       </c>
       <c r="C32" s="4">
-        <f>AVERAGE(C2:C8,C14:C18,C24:C26)</f>
-        <v>21.5333333333333</v>
+        <f>AVERAGE(C2:C9,C15:C16,C22:C26)</f>
+        <v>20.6</v>
       </c>
     </row>
   </sheetData>
@@ -1515,7 +1520,7 @@
         <v>2</v>
       </c>
       <c r="C2" s="1">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1526,7 +1531,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="1">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1534,22 +1539,16 @@
         <v>26</v>
       </c>
       <c r="B4" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C4" s="1">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B5" s="1">
-        <v>4</v>
-      </c>
-      <c r="C5" s="1">
-        <v>22</v>
-      </c>
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1"/>
@@ -1557,22 +1556,28 @@
       <c r="C6" s="1"/>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="1" t="s">
+      <c r="A7" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="1">
-        <f>AVERAGE(C2:C5)</f>
-        <v>21.75</v>
-      </c>
-      <c r="D8" s="2"/>
+      <c r="B7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="1">
+        <f>AVERAGE(C2:C4)</f>
+        <v>22.3333333333333</v>
+      </c>
+      <c r="D7" s="2"/>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" s="2">
+        <v>2</v>
+      </c>
+      <c r="C10" s="2">
+        <v>24</v>
+      </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
@@ -1582,7 +1587,7 @@
         <v>2</v>
       </c>
       <c r="C11" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1590,10 +1595,10 @@
         <v>29</v>
       </c>
       <c r="B12" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C12" s="2">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1604,7 +1609,7 @@
         <v>3</v>
       </c>
       <c r="C13" s="2">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1615,7 +1620,7 @@
         <v>3</v>
       </c>
       <c r="C14" s="2">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1623,10 +1628,10 @@
         <v>32</v>
       </c>
       <c r="B15" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" s="2">
-        <v>15</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -1634,22 +1639,16 @@
         <v>33</v>
       </c>
       <c r="B16" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C16" s="2">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B17" s="2">
-        <v>8</v>
-      </c>
-      <c r="C17" s="2">
-        <v>22</v>
-      </c>
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2"/>
@@ -1657,20 +1656,26 @@
       <c r="C18" s="2"/>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C20" s="2">
-        <f>AVERAGE(C11:C17)</f>
-        <v>21</v>
+      <c r="A19" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19" s="2">
+        <f>AVERAGE(C10:C16)</f>
+        <v>23.1428571428571</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B22" s="3">
+        <v>3</v>
+      </c>
+      <c r="C22" s="3">
+        <v>22</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1678,10 +1683,10 @@
         <v>35</v>
       </c>
       <c r="B23" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C23" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1689,10 +1694,10 @@
         <v>36</v>
       </c>
       <c r="B24" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C24" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1700,7 +1705,7 @@
         <v>37</v>
       </c>
       <c r="B25" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C25" s="3">
         <v>22</v>
@@ -1711,10 +1716,10 @@
         <v>38</v>
       </c>
       <c r="B26" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C26" s="3">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1729,14 +1734,14 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>21</v>
       </c>
       <c r="C29" s="3">
-        <f>AVERAGE(C23:C26)</f>
-        <v>21.75</v>
+        <f>AVERAGE(C22:C26)</f>
+        <v>22.8</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1747,8 +1752,8 @@
         <v>39</v>
       </c>
       <c r="C32" s="4">
-        <f>AVERAGE(C2:C5,C11:C17,C23:C26)</f>
-        <v>21.4</v>
+        <f>AVERAGE(C2:C4,C10:C16,C22:C26)</f>
+        <v>22.8666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -1784,10 +1789,10 @@
         <v>40</v>
       </c>
       <c r="B2" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C2" s="1">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1806,22 +1811,16 @@
         <v>42</v>
       </c>
       <c r="B4" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" s="1">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B5" s="1">
-        <v>3</v>
-      </c>
-      <c r="C5" s="1">
-        <v>22</v>
-      </c>
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1"/>
@@ -1829,32 +1828,38 @@
       <c r="C6" s="1"/>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="1" t="s">
+      <c r="A7" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="1">
-        <f>AVERAGE(C2:C5)</f>
-        <v>21.5</v>
-      </c>
-      <c r="D8" s="2"/>
+      <c r="B7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="1">
+        <f>AVERAGE(C2:C4)</f>
+        <v>23.3333333333333</v>
+      </c>
+      <c r="D7" s="2"/>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" s="2">
+        <v>1</v>
+      </c>
+      <c r="C10" s="2">
+        <v>22</v>
+      </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
         <v>44</v>
       </c>
       <c r="B11" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1865,7 +1870,7 @@
         <v>2</v>
       </c>
       <c r="C12" s="2">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1884,10 +1889,10 @@
         <v>47</v>
       </c>
       <c r="B14" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C14" s="2">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1898,7 +1903,7 @@
         <v>3</v>
       </c>
       <c r="C15" s="2">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -1909,7 +1914,7 @@
         <v>3</v>
       </c>
       <c r="C16" s="2">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1917,10 +1922,10 @@
         <v>50</v>
       </c>
       <c r="B17" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C17" s="2">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1942,7 +1947,7 @@
         <v>7</v>
       </c>
       <c r="C19" s="2">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1957,14 +1962,14 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C22" s="2">
-        <f>AVERAGE(C11:C19)</f>
-        <v>20.4444444444444</v>
+        <f>AVERAGE(C10:C19)</f>
+        <v>21.2</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1986,7 +1991,7 @@
         <v>4</v>
       </c>
       <c r="C26" s="3">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1997,7 +2002,7 @@
         <v>5</v>
       </c>
       <c r="C27" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -2023,14 +2028,14 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>21</v>
       </c>
       <c r="C31" s="3">
         <f>AVERAGE(C25:C28)</f>
-        <v>21.5</v>
+        <v>22.25</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -2041,8 +2046,8 @@
         <v>57</v>
       </c>
       <c r="C34" s="4">
-        <f>AVERAGE(C2:C5,C11:C19,C25:C28)</f>
-        <v>20.9411764705882</v>
+        <f>AVERAGE(C2:C4,C10:C19,C25:C28)</f>
+        <v>21.8235294117647</v>
       </c>
     </row>
   </sheetData>
@@ -2173,10 +2178,10 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C12" s="1">
         <f>AVERAGE(C2:C9)</f>
@@ -2240,10 +2245,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" s="2">
         <f>AVERAGE(C15:C18)</f>
@@ -2295,7 +2300,7 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>21</v>

--- a/src/views/game/zlzq/cardList/dahetaoCard/z_level.xlsx
+++ b/src/views/game/zlzq/cardList/dahetaoCard/z_level.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="11985" windowHeight="9795" firstSheet="1" activeTab="2"/>
+    <workbookView windowWidth="27945" windowHeight="12255" firstSheet="1" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="帝国" sheetId="5" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="75">
   <si>
     <t>名称</t>
   </si>
@@ -47,15 +47,15 @@
     <t>卡等</t>
   </si>
   <si>
-    <t>圣殿斥候</t>
-  </si>
-  <si>
     <t>圣殿卫士</t>
   </si>
   <si>
     <t>天使琼浆</t>
   </si>
   <si>
+    <t>炫目神光</t>
+  </si>
+  <si>
     <t>田园守望者1</t>
   </si>
   <si>
@@ -80,6 +80,9 @@
     <t>四芒军旗</t>
   </si>
   <si>
+    <t>圣殿御卫</t>
+  </si>
+  <si>
     <t>召集护卫</t>
   </si>
   <si>
@@ -89,9 +92,6 @@
     <t>曙光·安娜贝尔</t>
   </si>
   <si>
-    <t>圣枪·卡洛琳</t>
-  </si>
-  <si>
     <t>明日之音·露娜</t>
   </si>
   <si>
@@ -113,7 +113,10 @@
     <t>旷野猎手</t>
   </si>
   <si>
-    <t>势如破竹</t>
+    <t>势如破竹1</t>
+  </si>
+  <si>
+    <t>势如破竹2</t>
   </si>
   <si>
     <t>强行捕猎</t>
@@ -161,6 +164,9 @@
     <t>学仆-观测型</t>
   </si>
   <si>
+    <t>方尖魔碑</t>
+  </si>
+  <si>
     <t>沉重否定</t>
   </si>
   <si>
@@ -206,9 +212,6 @@
     <t>No.2时光·米拉</t>
   </si>
   <si>
-    <t>No.6沃凡瑞拉</t>
-  </si>
-  <si>
     <t>隐秘卡等：</t>
   </si>
   <si>
@@ -230,13 +233,13 @@
     <t>连击2</t>
   </si>
   <si>
+    <t>符文·疾风图腾</t>
+  </si>
+  <si>
     <t>铁山靠</t>
   </si>
   <si>
     <t>风卷残云</t>
-  </si>
-  <si>
-    <t>蟠桃隐士</t>
   </si>
   <si>
     <t>御风武者</t>
@@ -1245,10 +1248,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" s="1">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1259,7 +1262,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="1">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1270,7 +1273,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="1">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1281,7 +1284,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="1">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1292,7 +1295,7 @@
         <v>3</v>
       </c>
       <c r="C6" s="1">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1314,7 +1317,7 @@
         <v>5</v>
       </c>
       <c r="C8" s="1">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1347,7 +1350,7 @@
       </c>
       <c r="C12" s="1">
         <f>AVERAGE(C2:C9)</f>
-        <v>21.5</v>
+        <v>20.875</v>
       </c>
       <c r="D12" s="2"/>
     </row>
@@ -1359,7 +1362,7 @@
         <v>1</v>
       </c>
       <c r="C15" s="2">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -1367,16 +1370,22 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
+        <v>2</v>
+      </c>
+      <c r="C16" s="2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="2">
         <v>4</v>
       </c>
-      <c r="C16" s="2">
+      <c r="C17" s="2">
         <v>22</v>
       </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2"/>
@@ -1384,26 +1393,20 @@
       <c r="C18" s="2"/>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="2" t="s">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C19" s="2">
-        <f>AVERAGE(C15:C16)</f>
-        <v>20.5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="3" t="s">
+      <c r="B20" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B22" s="3">
-        <v>3</v>
-      </c>
-      <c r="C22" s="3">
-        <v>21</v>
+      <c r="C20" s="2">
+        <f>AVERAGE(C15:C17)</f>
+        <v>22.6666666666667</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1411,10 +1414,10 @@
         <v>17</v>
       </c>
       <c r="B23" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C23" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1425,7 +1428,7 @@
         <v>4</v>
       </c>
       <c r="C24" s="3">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1468,8 +1471,8 @@
         <v>21</v>
       </c>
       <c r="C29" s="3">
-        <f>AVERAGE(C22:C26)</f>
-        <v>19.2</v>
+        <f>AVERAGE(C23:C26)</f>
+        <v>20</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1480,8 +1483,8 @@
         <v>23</v>
       </c>
       <c r="C32" s="4">
-        <f>AVERAGE(C2:C9,C15:C16,C22:C26)</f>
-        <v>20.6</v>
+        <f>AVERAGE(C2:C9,C15:C17,C23:C26)</f>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -1493,7 +1496,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="16.375" customWidth="1"/>
@@ -1539,16 +1542,22 @@
         <v>26</v>
       </c>
       <c r="B4" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C4" s="1">
         <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
+      <c r="A5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="1">
+        <v>4</v>
+      </c>
+      <c r="C5" s="1">
+        <v>19</v>
+      </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1"/>
@@ -1556,28 +1565,22 @@
       <c r="C6" s="1"/>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B8" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="1">
-        <f>AVERAGE(C2:C4)</f>
-        <v>22.3333333333333</v>
-      </c>
-      <c r="D7" s="2"/>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B10" s="2">
-        <v>2</v>
-      </c>
-      <c r="C10" s="2">
-        <v>24</v>
-      </c>
+      <c r="C8" s="1">
+        <f>AVERAGE(C2:C5)</f>
+        <v>21.5</v>
+      </c>
+      <c r="D8" s="2"/>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
@@ -1587,7 +1590,7 @@
         <v>2</v>
       </c>
       <c r="C11" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1595,10 +1598,10 @@
         <v>29</v>
       </c>
       <c r="B12" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C12" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1620,7 +1623,7 @@
         <v>3</v>
       </c>
       <c r="C14" s="2">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1628,10 +1631,10 @@
         <v>32</v>
       </c>
       <c r="B15" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C15" s="2">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -1639,16 +1642,22 @@
         <v>33</v>
       </c>
       <c r="B16" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C16" s="2">
         <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
+      <c r="A17" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B17" s="2">
+        <v>8</v>
+      </c>
+      <c r="C17" s="2">
+        <v>24</v>
+      </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2"/>
@@ -1656,26 +1665,20 @@
       <c r="C18" s="2"/>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="2" t="s">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C19" s="2">
-        <f>AVERAGE(C10:C16)</f>
+      <c r="B20" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" s="2">
+        <f>AVERAGE(C11:C17)</f>
         <v>23.1428571428571</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B22" s="3">
-        <v>3</v>
-      </c>
-      <c r="C22" s="3">
-        <v>22</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1683,10 +1686,10 @@
         <v>35</v>
       </c>
       <c r="B23" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C23" s="3">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1694,7 +1697,7 @@
         <v>36</v>
       </c>
       <c r="B24" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C24" s="3">
         <v>23</v>
@@ -1705,10 +1708,10 @@
         <v>37</v>
       </c>
       <c r="B25" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C25" s="3">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1716,16 +1719,22 @@
         <v>38</v>
       </c>
       <c r="B26" s="3">
+        <v>6</v>
+      </c>
+      <c r="C26" s="3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" s="3">
         <v>7</v>
       </c>
-      <c r="C26" s="3">
+      <c r="C27" s="3">
         <v>24</v>
       </c>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27" s="3"/>
-      <c r="B27" s="3"/>
-      <c r="C27" s="3"/>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="3"/>
@@ -1733,27 +1742,32 @@
       <c r="C28" s="3"/>
     </row>
     <row r="29" spans="1:3">
-      <c r="A29" s="3" t="s">
+      <c r="A29" s="3"/>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B30" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C29" s="3">
-        <f>AVERAGE(C22:C26)</f>
-        <v>22.8</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3">
-      <c r="A32" s="4" t="s">
+      <c r="C30" s="3">
+        <f>AVERAGE(C23:C27)</f>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B32" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="C32" s="4">
-        <f>AVERAGE(C2:C4,C10:C16,C22:C26)</f>
-        <v>22.8666666666667</v>
+      <c r="B33" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C33" s="4">
+        <f>AVERAGE(C2:C5,C11:C17,C23:C27)</f>
+        <v>22.6875</v>
       </c>
     </row>
   </sheetData>
@@ -1786,7 +1800,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B2" s="1">
         <v>2</v>
@@ -1797,30 +1811,36 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B3" s="1">
         <v>2</v>
       </c>
       <c r="C3" s="1">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B4" s="1">
+        <v>2</v>
+      </c>
+      <c r="C4" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5" s="1">
         <v>3</v>
       </c>
-      <c r="C4" s="1">
+      <c r="C5" s="1">
         <v>24</v>
       </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1"/>
@@ -1828,35 +1848,29 @@
       <c r="C6" s="1"/>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B8" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="1">
-        <f>AVERAGE(C2:C4)</f>
-        <v>23.3333333333333</v>
-      </c>
-      <c r="D7" s="2"/>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B10" s="2">
-        <v>1</v>
-      </c>
-      <c r="C10" s="2">
-        <v>22</v>
-      </c>
+      <c r="C8" s="1">
+        <f>AVERAGE(C2:C5)</f>
+        <v>23.5</v>
+      </c>
+      <c r="D8" s="2"/>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B11" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C11" s="2">
         <v>23</v>
@@ -1864,18 +1878,18 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B12" s="2">
         <v>2</v>
       </c>
       <c r="C12" s="2">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B13" s="2">
         <v>2</v>
@@ -1886,18 +1900,18 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B14" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" s="2">
-        <v>24</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B15" s="2">
         <v>3</v>
@@ -1908,52 +1922,58 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B16" s="2">
         <v>3</v>
       </c>
       <c r="C16" s="2">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B17" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C17" s="2">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B18" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C18" s="2">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B19" s="2">
+        <v>5</v>
+      </c>
+      <c r="C19" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B20" s="2">
         <v>7</v>
       </c>
-      <c r="C19" s="2">
+      <c r="C20" s="2">
         <v>24</v>
       </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="2"/>
@@ -1961,59 +1981,53 @@
       <c r="C21" s="2"/>
     </row>
     <row r="22" spans="1:3">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C22" s="2">
-        <f>AVERAGE(C10:C19)</f>
-        <v>21.2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="B25" s="3">
-        <v>3</v>
-      </c>
-      <c r="C25" s="3">
-        <v>22</v>
+      <c r="B23" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" s="2">
+        <f>AVERAGE(C11:C20)</f>
+        <v>21.3</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B26" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C26" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B27" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C27" s="3">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B28" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C28" s="3">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -2034,8 +2048,8 @@
         <v>21</v>
       </c>
       <c r="C31" s="3">
-        <f>AVERAGE(C25:C28)</f>
-        <v>22.25</v>
+        <f>AVERAGE(C26:C28)</f>
+        <v>22.6666666666667</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -2043,11 +2057,11 @@
         <v>22</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C34" s="4">
-        <f>AVERAGE(C2:C4,C10:C19,C25:C28)</f>
-        <v>21.8235294117647</v>
+        <f>AVERAGE(C2:C5,C11:C20,C26:C28)</f>
+        <v>22.0588235294118</v>
       </c>
     </row>
   </sheetData>
@@ -2080,7 +2094,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B2" s="1">
         <v>1</v>
@@ -2091,18 +2105,18 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B3" s="1">
         <v>2</v>
       </c>
       <c r="C3" s="1">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B4" s="1">
         <v>2</v>
@@ -2113,18 +2127,18 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B5" s="1">
         <v>2</v>
       </c>
       <c r="C5" s="1">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B6" s="1">
         <v>3</v>
@@ -2135,7 +2149,7 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B7" s="1">
         <v>3</v>
@@ -2146,30 +2160,36 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B8" s="1">
         <v>3</v>
       </c>
       <c r="C8" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B9" s="1">
+        <v>3</v>
+      </c>
+      <c r="C9" s="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B10" s="1">
         <v>4</v>
       </c>
-      <c r="C9" s="1">
+      <c r="C10" s="1">
         <v>19</v>
       </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1"/>
@@ -2177,32 +2197,26 @@
       <c r="C11" s="1"/>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B13" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="1">
-        <f>AVERAGE(C2:C9)</f>
-        <v>18.625</v>
-      </c>
-      <c r="D12" s="2"/>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="B15" s="2">
-        <v>2</v>
-      </c>
-      <c r="C15" s="2">
-        <v>19</v>
-      </c>
+      <c r="C13" s="1">
+        <f>AVERAGE(C2:C10)</f>
+        <v>18.1111111111111</v>
+      </c>
+      <c r="D13" s="2"/>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B16" s="2">
         <v>4</v>
@@ -2213,7 +2227,7 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B17" s="2">
         <v>4</v>
@@ -2224,7 +2238,7 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B18" s="2">
         <v>5</v>
@@ -2248,16 +2262,16 @@
         <v>11</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C21" s="2">
-        <f>AVERAGE(C15:C18)</f>
-        <v>19.75</v>
+        <f>AVERAGE(C16:C18)</f>
+        <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B24" s="3">
         <v>3</v>
@@ -2268,18 +2282,18 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B25" s="3">
         <v>4</v>
       </c>
       <c r="C25" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B26" s="3">
         <v>4</v>
@@ -2307,7 +2321,7 @@
       </c>
       <c r="C29" s="3">
         <f>AVERAGE(C24:C26)</f>
-        <v>16</v>
+        <v>16.3333333333333</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -2315,11 +2329,11 @@
         <v>22</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C32" s="4">
-        <f>AVERAGE(C2:C9,C15:C18,C24:C26)</f>
-        <v>18.4</v>
+        <f>AVERAGE(C2:C10,C16:C18,C24:C26)</f>
+        <v>18.1333333333333</v>
       </c>
     </row>
   </sheetData>
